--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0007.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0007.xlsx
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Switch Weapons</t>
+          <t>Switch Vũ khí</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Switch Weapons</t>
+          <t>Switch Vũ khí</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
